--- a/план для сайта.xlsx
+++ b/план для сайта.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wwwor\OneDrive\Документы\GitHub\beer-abc-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82346344-B8B1-494E-A597-0BDBB18FD568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13532818-845C-4721-B347-345A93F3AD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="4590" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="4935" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="10">
   <si>
     <t>Октябрь 2025</t>
   </si>
@@ -72,7 +72,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -122,6 +122,22 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="PT Mono"/>
+      <family val="3"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="9">
@@ -174,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -262,11 +278,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -378,6 +439,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -600,7 +674,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2354,7 +2428,7 @@
     </row>
     <row r="115" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B115" s="35">
         <v>58354</v>
@@ -2371,7 +2445,7 @@
     </row>
     <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B116" s="35">
         <v>58354</v>
@@ -2388,7 +2462,7 @@
     </row>
     <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B117" s="35">
         <v>33170</v>
@@ -2405,7 +2479,7 @@
     </row>
     <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B118" s="35">
         <v>33170</v>
@@ -2422,7 +2496,7 @@
     </row>
     <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B119" s="35">
         <v>33270</v>
@@ -2439,7 +2513,7 @@
     </row>
     <row r="120" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B120" s="35">
         <v>39803</v>
@@ -2454,9 +2528,9 @@
         <v>27864</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A121" s="14">
-        <v>7</v>
+    <row r="121" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A121" s="18">
+        <v>8</v>
       </c>
       <c r="B121" s="35">
         <v>39803</v>
@@ -2472,9 +2546,9 @@
       </c>
       <c r="I121" s="42"/>
     </row>
-    <row r="122" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A122" s="18">
-        <v>8</v>
+    <row r="122" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A122" s="14">
+        <v>9</v>
       </c>
       <c r="B122" s="35">
         <v>58354</v>
@@ -2491,7 +2565,7 @@
     </row>
     <row r="123" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B123" s="35">
         <v>58354</v>
@@ -2508,7 +2582,7 @@
     </row>
     <row r="124" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B124" s="35">
         <v>33170</v>
@@ -2525,7 +2599,7 @@
     </row>
     <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B125" s="35">
         <v>33170</v>
@@ -2542,7 +2616,7 @@
     </row>
     <row r="126" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B126" s="35">
         <v>33100</v>
@@ -2559,7 +2633,7 @@
     </row>
     <row r="127" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B127" s="35">
         <v>39803</v>
@@ -2576,7 +2650,7 @@
     </row>
     <row r="128" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B128" s="35">
         <v>39803</v>
@@ -2593,7 +2667,7 @@
     </row>
     <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B129" s="35">
         <v>58354</v>
@@ -2610,7 +2684,7 @@
     </row>
     <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B130" s="35">
         <v>58354</v>
@@ -2627,7 +2701,7 @@
     </row>
     <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B131" s="35">
         <v>33170</v>
@@ -2644,7 +2718,7 @@
     </row>
     <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B132" s="35">
         <v>33170</v>
@@ -2661,7 +2735,7 @@
     </row>
     <row r="133" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B133" s="35">
         <v>33170</v>
@@ -2678,7 +2752,7 @@
     </row>
     <row r="134" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B134" s="35">
         <v>39803</v>
@@ -2695,7 +2769,7 @@
     </row>
     <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B135" s="35">
         <v>39803</v>
@@ -2712,7 +2786,7 @@
     </row>
     <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B136" s="35">
         <v>58354</v>
@@ -2729,7 +2803,7 @@
     </row>
     <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B137" s="35">
         <v>58354</v>
@@ -2746,7 +2820,7 @@
     </row>
     <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B138" s="35">
         <v>33170</v>
@@ -2763,7 +2837,7 @@
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B139" s="35">
         <v>33170</v>
@@ -2780,7 +2854,7 @@
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B140" s="35">
         <v>33170</v>
@@ -2797,7 +2871,7 @@
     </row>
     <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B141" s="35">
         <v>39803</v>
@@ -2814,7 +2888,7 @@
     </row>
     <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B142" s="35">
         <v>39803</v>
@@ -2829,9 +2903,9 @@
         <v>27864</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A143" s="14">
-        <v>29</v>
+    <row r="143" spans="1:5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="19">
+        <v>30</v>
       </c>
       <c r="B143" s="35">
         <v>58354</v>
@@ -2846,9 +2920,9 @@
         <v>40852</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A144" s="19">
-        <v>30</v>
+    <row r="144" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="14">
+        <v>31</v>
       </c>
       <c r="B144" s="37">
         <v>58354</v>
@@ -2863,13 +2937,532 @@
         <v>40852</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A145" s="23"/>
       <c r="B145" s="42"/>
       <c r="C145" s="42"/>
       <c r="D145" s="42"/>
       <c r="E145" s="42"/>
     </row>
+    <row r="146" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B146" s="47">
+        <v>46054</v>
+      </c>
+      <c r="C146" s="47">
+        <v>46054</v>
+      </c>
+      <c r="D146" s="47">
+        <v>46054</v>
+      </c>
+      <c r="E146" s="47">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D147" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B148" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="14">
+        <v>1</v>
+      </c>
+      <c r="B149" s="43">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C149" s="43">
+        <v>24.38</v>
+      </c>
+      <c r="D149" s="43">
+        <v>24.94</v>
+      </c>
+      <c r="E149" s="43">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="14">
+        <v>2</v>
+      </c>
+      <c r="B150" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C150" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D150" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E150" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="14">
+        <v>3</v>
+      </c>
+      <c r="B151" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C151" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D151" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E151" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="14">
+        <v>4</v>
+      </c>
+      <c r="B152" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C152" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D152" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E152" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="14">
+        <v>5</v>
+      </c>
+      <c r="B153" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C153" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D153" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E153" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="14">
+        <v>6</v>
+      </c>
+      <c r="B154" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C154" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D154" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E154" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="14">
+        <v>7</v>
+      </c>
+      <c r="B155" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C155" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D155" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E155" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="18">
+        <v>8</v>
+      </c>
+      <c r="B156" s="45">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C156" s="45">
+        <v>24.38</v>
+      </c>
+      <c r="D156" s="45">
+        <v>24.94</v>
+      </c>
+      <c r="E156" s="45">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="14">
+        <v>9</v>
+      </c>
+      <c r="B157" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C157" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D157" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E157" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="14">
+        <v>10</v>
+      </c>
+      <c r="B158" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C158" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D158" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E158" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="14">
+        <v>11</v>
+      </c>
+      <c r="B159" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C159" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D159" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E159" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="14">
+        <v>12</v>
+      </c>
+      <c r="B160" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C160" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D160" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E160" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="14">
+        <v>13</v>
+      </c>
+      <c r="B161" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C161" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D161" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E161" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="14">
+        <v>14</v>
+      </c>
+      <c r="B162" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C162" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D162" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E162" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="14">
+        <v>15</v>
+      </c>
+      <c r="B163" s="45">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C163" s="45">
+        <v>24.38</v>
+      </c>
+      <c r="D163" s="45">
+        <v>24.94</v>
+      </c>
+      <c r="E163" s="45">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="14">
+        <v>16</v>
+      </c>
+      <c r="B164" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C164" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D164" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E164" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="14">
+        <v>17</v>
+      </c>
+      <c r="B165" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C165" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D165" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E165" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="14">
+        <v>18</v>
+      </c>
+      <c r="B166" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C166" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D166" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E166" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="14">
+        <v>19</v>
+      </c>
+      <c r="B167" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C167" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D167" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E167" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="14">
+        <v>20</v>
+      </c>
+      <c r="B168" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C168" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D168" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E168" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="14">
+        <v>21</v>
+      </c>
+      <c r="B169" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C169" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D169" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E169" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="14">
+        <v>22</v>
+      </c>
+      <c r="B170" s="45">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C170" s="45">
+        <v>24.38</v>
+      </c>
+      <c r="D170" s="45">
+        <v>24.94</v>
+      </c>
+      <c r="E170" s="45">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="14">
+        <v>23</v>
+      </c>
+      <c r="B171" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C171" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D171" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E171" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="14">
+        <v>24</v>
+      </c>
+      <c r="B172" s="44">
+        <v>35.024999999999999</v>
+      </c>
+      <c r="C172" s="44">
+        <v>24.38</v>
+      </c>
+      <c r="D172" s="44">
+        <v>24.94</v>
+      </c>
+      <c r="E172" s="44">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="14">
+        <v>25</v>
+      </c>
+      <c r="B173" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C173" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D173" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E173" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="14">
+        <v>26</v>
+      </c>
+      <c r="B174" s="44">
+        <v>42.03</v>
+      </c>
+      <c r="C174" s="44">
+        <v>29.256</v>
+      </c>
+      <c r="D174" s="44">
+        <v>29.928000000000001</v>
+      </c>
+      <c r="E174" s="44">
+        <v>29.928000000000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="14">
+        <v>27</v>
+      </c>
+      <c r="B175" s="44">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C175" s="44">
+        <v>42.92</v>
+      </c>
+      <c r="D175" s="44">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E175" s="44">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="14">
+        <v>28</v>
+      </c>
+      <c r="B176" s="45">
+        <v>61.658999999999999</v>
+      </c>
+      <c r="C176" s="45">
+        <v>42.92</v>
+      </c>
+      <c r="D176" s="45">
+        <v>43.905999999999999</v>
+      </c>
+      <c r="E176" s="45">
+        <v>43.905999999999999</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
